--- a/artfynd/A 11878-2023 artfynd.xlsx
+++ b/artfynd/A 11878-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11878-2023 artfynd.xlsx
+++ b/artfynd/A 11878-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1965,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113190256</v>
+        <v>113246276</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
+        <v>97628</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,41 +1977,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrgården, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666863</v>
+        <v>666640</v>
       </c>
       <c r="R13" t="n">
-        <v>6707038</v>
+        <v>6707122</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2033,19 +2033,14 @@
           <t>Hållnäs</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>C-Tie-0465</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,23 +2055,23 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alex Karlstens</t>
+          <t>Cecilia Rätz, Dennis Nyström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113246276</v>
+        <v>113246269</v>
       </c>
       <c r="B14" t="n">
         <v>97628</v>
@@ -2116,10 +2111,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666640</v>
+        <v>666588</v>
       </c>
       <c r="R14" t="n">
-        <v>6707122</v>
+        <v>6707191</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2182,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113246269</v>
+        <v>113246256</v>
       </c>
       <c r="B15" t="n">
-        <v>97628</v>
+        <v>90105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2198,21 +2193,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>3215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2222,10 +2217,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666588</v>
+        <v>666685</v>
       </c>
       <c r="R15" t="n">
-        <v>6707191</v>
+        <v>6706867</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2288,7 +2283,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113246256</v>
+        <v>113246296</v>
       </c>
       <c r="B16" t="n">
         <v>90105</v>
@@ -2328,10 +2323,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666685</v>
+        <v>667015</v>
       </c>
       <c r="R16" t="n">
-        <v>6706867</v>
+        <v>6707008</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2394,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113246296</v>
+        <v>113246295</v>
       </c>
       <c r="B17" t="n">
-        <v>90105</v>
+        <v>99909</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2410,21 +2405,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2434,10 +2429,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>667015</v>
+        <v>667018</v>
       </c>
       <c r="R17" t="n">
-        <v>6707008</v>
+        <v>6707015</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2500,10 +2495,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113246295</v>
+        <v>113246275</v>
       </c>
       <c r="B18" t="n">
-        <v>99909</v>
+        <v>90105</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,21 +2511,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2540,10 +2535,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>667018</v>
+        <v>666637</v>
       </c>
       <c r="R18" t="n">
-        <v>6707015</v>
+        <v>6707126</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2601,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113246275</v>
+        <v>113246282</v>
       </c>
       <c r="B19" t="n">
         <v>90105</v>
@@ -2646,10 +2641,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>666637</v>
+        <v>666617</v>
       </c>
       <c r="R19" t="n">
-        <v>6707126</v>
+        <v>6707043</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2712,10 +2707,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113246282</v>
+        <v>113243310</v>
       </c>
       <c r="B20" t="n">
-        <v>90105</v>
+        <v>99909</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2728,21 +2723,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2752,10 +2747,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>666617</v>
+        <v>666822</v>
       </c>
       <c r="R20" t="n">
-        <v>6707043</v>
+        <v>6707055</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2798,6 +2793,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2818,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113243310</v>
+        <v>113246266</v>
       </c>
       <c r="B21" t="n">
-        <v>99909</v>
+        <v>96610</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>666822</v>
+        <v>666549</v>
       </c>
       <c r="R21" t="n">
-        <v>6707055</v>
+        <v>6707239</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2904,11 +2904,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>Cecilia Rätz</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2929,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113246266</v>
+        <v>113246286</v>
       </c>
       <c r="B22" t="n">
-        <v>96610</v>
+        <v>109757</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2945,16 +2940,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>219711</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2969,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>666549</v>
+        <v>666957</v>
       </c>
       <c r="R22" t="n">
-        <v>6707239</v>
+        <v>6707150</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3035,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113246286</v>
+        <v>113246277</v>
       </c>
       <c r="B23" t="n">
-        <v>109757</v>
+        <v>97628</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3051,21 +3046,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3075,10 +3070,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>666957</v>
+        <v>666628</v>
       </c>
       <c r="R23" t="n">
-        <v>6707150</v>
+        <v>6707103</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,10 +3136,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113246277</v>
+        <v>113246312</v>
       </c>
       <c r="B24" t="n">
-        <v>97628</v>
+        <v>97650</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3153,38 +3148,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>666628</v>
+        <v>666860</v>
       </c>
       <c r="R24" t="n">
-        <v>6707103</v>
+        <v>6707028</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3247,10 +3246,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113246312</v>
+        <v>113246307</v>
       </c>
       <c r="B25" t="n">
-        <v>97650</v>
+        <v>90774</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,38 +3262,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>666860</v>
+        <v>666900</v>
       </c>
       <c r="R25" t="n">
-        <v>6707028</v>
+        <v>6706964</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3357,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113246307</v>
+        <v>113246263</v>
       </c>
       <c r="B26" t="n">
-        <v>90774</v>
+        <v>86180</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3369,25 +3364,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>3674</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3397,10 +3392,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>666900</v>
+        <v>666579</v>
       </c>
       <c r="R26" t="n">
-        <v>6706964</v>
+        <v>6707130</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3463,10 +3458,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113246263</v>
+        <v>113246281</v>
       </c>
       <c r="B27" t="n">
-        <v>86180</v>
+        <v>90105</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3479,21 +3474,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3503,10 +3498,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>666579</v>
+        <v>666636</v>
       </c>
       <c r="R27" t="n">
-        <v>6707130</v>
+        <v>6707097</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,10 +3564,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113246281</v>
+        <v>113246310</v>
       </c>
       <c r="B28" t="n">
-        <v>90105</v>
+        <v>99909</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3585,21 +3580,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3609,10 +3604,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>666636</v>
+        <v>666894</v>
       </c>
       <c r="R28" t="n">
-        <v>6707097</v>
+        <v>6706966</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,10 +3670,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113246310</v>
+        <v>113246291</v>
       </c>
       <c r="B29" t="n">
-        <v>99909</v>
+        <v>90105</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3691,21 +3686,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,10 +3710,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>666894</v>
+        <v>667019</v>
       </c>
       <c r="R29" t="n">
-        <v>6706966</v>
+        <v>6707080</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3781,10 +3776,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113246291</v>
+        <v>113246300</v>
       </c>
       <c r="B30" t="n">
-        <v>90105</v>
+        <v>99909</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3797,21 +3792,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3821,10 +3816,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>667019</v>
+        <v>666990</v>
       </c>
       <c r="R30" t="n">
-        <v>6707080</v>
+        <v>6706967</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3887,10 +3882,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113246300</v>
+        <v>113246267</v>
       </c>
       <c r="B31" t="n">
-        <v>99909</v>
+        <v>86180</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3903,21 +3898,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3927,10 +3922,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>666990</v>
+        <v>666570</v>
       </c>
       <c r="R31" t="n">
-        <v>6706967</v>
+        <v>6707259</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3993,10 +3988,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113246267</v>
+        <v>113246292</v>
       </c>
       <c r="B32" t="n">
-        <v>86180</v>
+        <v>90105</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4009,21 +4004,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4033,10 +4028,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>666570</v>
+        <v>667008</v>
       </c>
       <c r="R32" t="n">
-        <v>6707259</v>
+        <v>6707042</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4099,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113246292</v>
+        <v>113243308</v>
       </c>
       <c r="B33" t="n">
-        <v>90105</v>
+        <v>97650</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4111,38 +4106,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>667008</v>
+        <v>666865</v>
       </c>
       <c r="R33" t="n">
-        <v>6707042</v>
+        <v>6707016</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,6 +4184,11 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4205,10 +4209,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113243308</v>
+        <v>113246255</v>
       </c>
       <c r="B34" t="n">
-        <v>97650</v>
+        <v>86180</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4217,42 +4221,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>666865</v>
+        <v>666657</v>
       </c>
       <c r="R34" t="n">
-        <v>6707016</v>
+        <v>6706776</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4295,11 +4295,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>Cecilia Rätz</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4320,10 +4315,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113246255</v>
+        <v>113246271</v>
       </c>
       <c r="B35" t="n">
-        <v>86180</v>
+        <v>97628</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4336,21 +4331,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4360,10 +4355,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>666657</v>
+        <v>666600</v>
       </c>
       <c r="R35" t="n">
-        <v>6706776</v>
+        <v>6707176</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4426,10 +4421,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113246271</v>
+        <v>113246278</v>
       </c>
       <c r="B36" t="n">
-        <v>97628</v>
+        <v>99909</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4442,21 +4437,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4466,10 +4461,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>666600</v>
+        <v>666633</v>
       </c>
       <c r="R36" t="n">
-        <v>6707176</v>
+        <v>6707106</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4532,10 +4527,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113246278</v>
+        <v>113246283</v>
       </c>
       <c r="B37" t="n">
-        <v>99909</v>
+        <v>96610</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4548,21 +4543,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4572,10 +4567,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>666633</v>
+        <v>666807</v>
       </c>
       <c r="R37" t="n">
-        <v>6707106</v>
+        <v>6707079</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4638,10 +4633,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113246283</v>
+        <v>113246274</v>
       </c>
       <c r="B38" t="n">
-        <v>96610</v>
+        <v>90105</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4654,21 +4649,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4678,10 +4673,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>666807</v>
+        <v>666645</v>
       </c>
       <c r="R38" t="n">
-        <v>6707079</v>
+        <v>6707129</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4744,7 +4739,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113246274</v>
+        <v>113246258</v>
       </c>
       <c r="B39" t="n">
         <v>90105</v>
@@ -4784,10 +4779,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>666645</v>
+        <v>666653</v>
       </c>
       <c r="R39" t="n">
-        <v>6707129</v>
+        <v>6707030</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4843,112 +4838,6 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr">
-        <is>
-          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>113246258</v>
-      </c>
-      <c r="B40" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>3215</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Rödgul trumpetsvamp</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Craterellus lutescens</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Göksnåre, Upl</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>666653</v>
-      </c>
-      <c r="R40" t="n">
-        <v>6707030</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Tierp</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Hållnäs</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2023-10-11</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2023-10-11</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Axel Linder</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Cecilia Rätz, Dennis Nyström</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
         <is>
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
